--- a/2026/CABRERA/Mayo/Mayo CABRERA.xlsx
+++ b/2026/CABRERA/Mayo/Mayo CABRERA.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24334"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistema\Desktop\rc-consorcio2025\2026\CABRERA\Mayo\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistemax\Desktop\rc-consorcio2025\2026\CABRERA\Mayo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1F5BEB7-F567-4FE8-BBB7-D7ACA09C72A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60C36BD2-DC8B-4289-9305-FC797002A6FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="793" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="793" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RESUMEN" sheetId="1" r:id="rId1"/>
@@ -19,14 +19,19 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="1">PRORRATEO!$A$1:$O$26</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$D$96</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$D$95</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
+  <extLst>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="137">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="134">
   <si>
     <t>TOTAL SUELDO</t>
   </si>
@@ -347,9 +352,6 @@
   </si>
   <si>
     <t>Acosta Cristian</t>
-  </si>
-  <si>
-    <t>Ezequiel</t>
   </si>
   <si>
     <t>JAUREGUIBERRY, Candela</t>
@@ -403,24 +405,9 @@
     <t>Lucas damian rivero</t>
   </si>
   <si>
-    <t>Transf 06/04</t>
-  </si>
-  <si>
-    <t>Servicio de cerrajeria, extraccion de llave trabada en el cilindro de la puerta de reja</t>
-  </si>
-  <si>
     <t>Transf 08/04</t>
   </si>
   <si>
-    <t>Debito 06/04</t>
-  </si>
-  <si>
-    <t>Servicio de cerrajeria, cerradura angosta colocada</t>
-  </si>
-  <si>
-    <t>Transf 13/04</t>
-  </si>
-  <si>
     <t>Abdon alberto</t>
   </si>
   <si>
@@ -440,6 +427,15 @@
   </si>
   <si>
     <t>Transf 08/05</t>
+  </si>
+  <si>
+    <t>Debito 05/05</t>
+  </si>
+  <si>
+    <t>Transf 11/05</t>
+  </si>
+  <si>
+    <t>Ezequiel Mazzio</t>
   </si>
 </sst>
 </file>
@@ -453,7 +449,7 @@
     <numFmt numFmtId="164" formatCode="_ &quot;$&quot;\ * #,##0.00_ ;_ &quot;$&quot;\ * \-#,##0.00_ ;_ &quot;$&quot;\ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="165" formatCode="_-&quot;$&quot;\ * #,##0_-;\-&quot;$&quot;\ * #,##0_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="23" x14ac:knownFonts="1">
+  <fonts count="22" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -619,13 +615,6 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
   <fills count="12">
     <fill>
@@ -1054,7 +1043,7 @@
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="181">
+  <cellXfs count="180">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -1298,6 +1287,45 @@
     <xf numFmtId="0" fontId="15" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="9" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1340,50 +1368,10 @@
     <xf numFmtId="0" fontId="11" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="8" fontId="22" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="8" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="8" fontId="22" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="22" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="4" fillId="9" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Moneda" xfId="1" builtinId="4"/>
@@ -1452,9 +1440,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema de Office">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1492,9 +1480,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1527,9 +1515,26 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1562,9 +1567,26 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1738,21 +1760,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L96"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:L95"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="37.5546875" customWidth="1"/>
-    <col min="2" max="2" width="24.6640625" customWidth="1"/>
-    <col min="3" max="3" width="18.44140625" customWidth="1"/>
-    <col min="4" max="4" width="15.6640625" customWidth="1"/>
-    <col min="5" max="5" width="14.5546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.109375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="42.33203125" customWidth="1"/>
+    <col min="1" max="1" width="37.5703125" customWidth="1"/>
+    <col min="2" max="2" width="24.7109375" customWidth="1"/>
+    <col min="3" max="3" width="18.42578125" customWidth="1"/>
+    <col min="4" max="4" width="15.7109375" customWidth="1"/>
+    <col min="5" max="5" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="42.28515625" customWidth="1"/>
     <col min="10" max="10" width="18" customWidth="1"/>
-    <col min="11" max="11" width="18.33203125" customWidth="1"/>
+    <col min="11" max="11" width="18.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="82" t="s">
         <v>50</v>
       </c>
@@ -1760,7 +1782,7 @@
       <c r="C1" s="3"/>
       <c r="D1" s="3"/>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="78" t="s">
         <v>102</v>
       </c>
@@ -1768,7 +1790,7 @@
       <c r="C2" s="78"/>
       <c r="D2" s="78"/>
     </row>
-    <row r="3" spans="1:8" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:8" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="78" t="s">
         <v>57</v>
       </c>
@@ -1776,44 +1798,44 @@
       <c r="C3" s="78"/>
       <c r="D3" s="78"/>
     </row>
-    <row r="4" spans="1:8" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:8" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="142" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B4" s="142"/>
       <c r="C4" s="79"/>
       <c r="D4" s="79"/>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="142"/>
       <c r="B5" s="142"/>
       <c r="C5" s="79"/>
       <c r="D5" s="79"/>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="142"/>
       <c r="B6" s="142"/>
       <c r="C6" s="79"/>
       <c r="D6" s="79"/>
     </row>
-    <row r="7" spans="1:8" ht="6.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:8" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="142"/>
       <c r="B7" s="142"/>
       <c r="C7" s="79"/>
       <c r="D7" s="79"/>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B9" s="150" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B10" s="150"/>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B11" s="150"/>
     </row>
-    <row r="13" spans="1:8" ht="14.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:8" ht="14.45" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="F13" t="s">
         <v>99</v>
       </c>
@@ -1824,7 +1846,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="14" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="143" t="s">
         <v>49</v>
       </c>
@@ -1832,30 +1854,30 @@
       <c r="C14" s="143"/>
       <c r="D14" s="143"/>
     </row>
-    <row r="15" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="143"/>
       <c r="B15" s="143"/>
       <c r="C15" s="143"/>
       <c r="D15" s="143"/>
     </row>
-    <row r="16" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="143"/>
       <c r="B16" s="143"/>
       <c r="C16" s="143"/>
       <c r="D16" s="143"/>
     </row>
-    <row r="17" spans="1:7" ht="53.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7" ht="53.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="143"/>
       <c r="B17" s="143"/>
       <c r="C17" s="143"/>
       <c r="D17" s="143"/>
     </row>
-    <row r="18" spans="1:7" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="19" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:7" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="19" spans="1:7" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A19" s="1"/>
     </row>
-    <row r="20" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="6" t="s">
         <v>15</v>
       </c>
@@ -1863,7 +1885,7 @@
       <c r="C21" s="5"/>
       <c r="D21" s="8"/>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="15" t="s">
         <v>40</v>
       </c>
@@ -1871,43 +1893,43 @@
       <c r="C22" s="13"/>
       <c r="D22" s="13"/>
     </row>
-    <row r="23" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
         <v>104</v>
       </c>
       <c r="B23" s="2"/>
-      <c r="C23" s="179">
+      <c r="C23" s="92">
         <v>475000</v>
       </c>
       <c r="D23" s="85" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A24" s="2"/>
       <c r="B24" s="2"/>
       <c r="C24" s="92"/>
       <c r="D24" s="81"/>
     </row>
-    <row r="25" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A25" s="2"/>
       <c r="B25" s="2"/>
       <c r="C25" s="92"/>
       <c r="D25" s="81"/>
     </row>
-    <row r="26" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A26" s="2"/>
       <c r="B26" s="2"/>
       <c r="C26" s="92"/>
       <c r="D26" s="81"/>
     </row>
-    <row r="27" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A27" s="2"/>
       <c r="B27" s="2"/>
       <c r="C27" s="93"/>
       <c r="D27" s="81"/>
     </row>
-    <row r="28" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A28" s="29" t="s">
         <v>41</v>
       </c>
@@ -1918,7 +1940,7 @@
       </c>
       <c r="D28" s="54"/>
     </row>
-    <row r="29" spans="1:7" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:7" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A29" s="11" t="s">
         <v>0</v>
       </c>
@@ -1931,7 +1953,7 @@
       <c r="E29" s="9"/>
       <c r="F29" s="9"/>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" s="15" t="s">
         <v>26</v>
       </c>
@@ -1940,20 +1962,20 @@
       <c r="D30" s="56"/>
       <c r="F30" s="9"/>
     </row>
-    <row r="31" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="118" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="B31" s="119"/>
       <c r="C31" s="178">
         <v>102000</v>
       </c>
       <c r="D31" s="90" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="G31" s="9"/>
     </row>
-    <row r="32" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A32" s="14" t="s">
         <v>22</v>
       </c>
@@ -1964,7 +1986,7 @@
         <v>102000</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="13" t="s">
         <v>37</v>
       </c>
@@ -1972,19 +1994,19 @@
       <c r="C33" s="17"/>
       <c r="D33" s="37"/>
     </row>
-    <row r="34" spans="1:6" s="22" customFormat="1" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:6" s="22" customFormat="1" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="148" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B34" s="149"/>
       <c r="C34" s="112">
         <v>87769</v>
       </c>
       <c r="D34" s="89" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6" ht="14.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" ht="14.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A35" s="14" t="s">
         <v>1</v>
       </c>
@@ -1995,7 +2017,7 @@
         <v>87769</v>
       </c>
     </row>
-    <row r="36" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A36" s="13" t="s">
         <v>23</v>
       </c>
@@ -2003,48 +2025,48 @@
       <c r="C36" s="20"/>
       <c r="D36" s="58"/>
     </row>
-    <row r="37" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A37" s="53" t="s">
         <v>51</v>
       </c>
       <c r="B37" s="53" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="C37" s="113"/>
       <c r="D37" s="89"/>
       <c r="F37" s="83"/>
     </row>
-    <row r="38" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A38" s="53" t="s">
         <v>52</v>
       </c>
       <c r="B38" s="53" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="C38" s="94"/>
       <c r="D38" s="89"/>
     </row>
-    <row r="39" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A39" s="53" t="s">
         <v>53</v>
       </c>
       <c r="B39" s="53" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="C39" s="94"/>
       <c r="D39" s="89"/>
     </row>
-    <row r="40" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A40" s="53" t="s">
         <v>54</v>
       </c>
       <c r="B40" s="53" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="C40" s="94"/>
       <c r="D40" s="88"/>
     </row>
-    <row r="41" spans="1:6" ht="15" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:6" ht="15" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A41" s="14" t="s">
         <v>2</v>
       </c>
@@ -2055,7 +2077,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" s="13" t="s">
         <v>25</v>
       </c>
@@ -2063,43 +2085,43 @@
       <c r="C42" s="20"/>
       <c r="D42" s="58"/>
     </row>
-    <row r="43" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="68" t="s">
         <v>96</v>
       </c>
       <c r="B43" s="53"/>
-      <c r="C43" s="180">
+      <c r="C43" s="94">
         <v>96924.479999999996</v>
       </c>
       <c r="D43" s="87" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="44" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="53" t="s">
         <v>95</v>
       </c>
       <c r="B44" s="53"/>
       <c r="C44" s="94">
-        <v>154799.45000000001</v>
+        <v>205492.85</v>
       </c>
       <c r="D44" s="87" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="53" t="s">
         <v>103</v>
       </c>
       <c r="B45" s="53"/>
-      <c r="C45" s="180">
+      <c r="C45" s="94">
         <v>324588.2</v>
       </c>
       <c r="D45" s="87" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A46" s="14" t="s">
         <v>3</v>
       </c>
@@ -2107,10 +2129,10 @@
       <c r="C46" s="19"/>
       <c r="D46" s="57">
         <f>SUM(C43:C45)</f>
-        <v>576312.13</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <v>627005.53</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A47" s="13" t="s">
         <v>24</v>
       </c>
@@ -2118,394 +2140,375 @@
       <c r="C47" s="19"/>
       <c r="D47" s="60"/>
     </row>
-    <row r="48" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="148" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B48" s="149"/>
       <c r="C48" s="94">
         <v>73200</v>
       </c>
       <c r="D48" s="85" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="49" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A49" s="122" t="s">
-        <v>128</v>
-      </c>
+        <v>123</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A49" s="122"/>
       <c r="B49" s="120"/>
-      <c r="C49" s="94">
-        <v>84000</v>
-      </c>
-      <c r="D49" s="87" t="s">
-        <v>124</v>
-      </c>
+      <c r="C49" s="94"/>
+      <c r="D49" s="87"/>
       <c r="E49" s="25"/>
     </row>
-    <row r="50" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A50" s="148" t="s">
-        <v>125</v>
-      </c>
-      <c r="B50" s="149"/>
-      <c r="C50" s="94">
-        <v>65000</v>
-      </c>
-      <c r="D50" s="87" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="51" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A51" s="14" t="s">
+    <row r="50" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A50" s="14" t="s">
         <v>8</v>
       </c>
-      <c r="B51" s="13"/>
-      <c r="C51" s="13"/>
-      <c r="D51" s="63">
-        <f>SUM(C48:C50)</f>
-        <v>222200</v>
-      </c>
-    </row>
-    <row r="52" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A52" s="13" t="s">
+      <c r="B50" s="13"/>
+      <c r="C50" s="13"/>
+      <c r="D50" s="63">
+        <f>SUM(C48:C49)</f>
+        <v>73200</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A51" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="B52" s="123"/>
-      <c r="C52" s="12"/>
-      <c r="D52" s="60"/>
-    </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B51" s="123"/>
+      <c r="C51" s="12"/>
+      <c r="D51" s="60"/>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A52" s="53" t="s">
+        <v>98</v>
+      </c>
+      <c r="B52" s="53"/>
+      <c r="C52" s="94">
+        <v>69000</v>
+      </c>
+      <c r="D52" s="64"/>
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" s="53" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B53" s="53"/>
-      <c r="C53" s="94">
-        <v>57500</v>
-      </c>
-      <c r="D53" s="64"/>
-    </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A54" s="53" t="s">
-        <v>97</v>
-      </c>
-      <c r="B54" s="53"/>
-      <c r="C54" s="94">
+      <c r="C53" s="179">
         <v>37161.9</v>
       </c>
-      <c r="D54" s="62"/>
-    </row>
-    <row r="55" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A55" s="124" t="s">
+      <c r="D53" s="62"/>
+    </row>
+    <row r="54" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A54" s="124" t="s">
         <v>22</v>
       </c>
-      <c r="B55" s="124"/>
-      <c r="C55" s="65"/>
-      <c r="D55" s="57">
-        <f>SUM(C53:C54)</f>
-        <v>94661.9</v>
-      </c>
-    </row>
-    <row r="56" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A56" s="53"/>
-      <c r="B56" s="53"/>
-      <c r="C56" s="53"/>
-      <c r="D56" s="66"/>
-    </row>
-    <row r="57" spans="1:6" ht="22.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A57" s="144" t="s">
-        <v>119</v>
-      </c>
-      <c r="B57" s="145"/>
-      <c r="C57" s="146"/>
-      <c r="D57" s="67"/>
-    </row>
-    <row r="58" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A58" s="125"/>
-      <c r="B58" s="68"/>
-      <c r="C58" s="68"/>
-      <c r="D58" s="69"/>
+      <c r="B54" s="124"/>
+      <c r="C54" s="65"/>
+      <c r="D54" s="57">
+        <f>SUM(C52:C53)</f>
+        <v>106161.9</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A55" s="53"/>
+      <c r="B55" s="53"/>
+      <c r="C55" s="53"/>
+      <c r="D55" s="66"/>
+    </row>
+    <row r="56" spans="1:6" ht="22.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A56" s="144" t="s">
+        <v>118</v>
+      </c>
+      <c r="B56" s="145"/>
+      <c r="C56" s="146"/>
+      <c r="D56" s="67"/>
+    </row>
+    <row r="57" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A57" s="125"/>
+      <c r="B57" s="68"/>
+      <c r="C57" s="68"/>
+      <c r="D57" s="69"/>
+      <c r="E57" s="25"/>
+    </row>
+    <row r="58" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A58" s="126" t="s">
+        <v>19</v>
+      </c>
+      <c r="B58" s="127"/>
+      <c r="C58" s="70"/>
+      <c r="D58" s="71">
+        <f>(SUM(D24:D56))</f>
+        <v>1471136.43</v>
+      </c>
       <c r="E58" s="25"/>
-    </row>
-    <row r="59" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A59" s="126" t="s">
-        <v>19</v>
-      </c>
-      <c r="B59" s="127"/>
-      <c r="C59" s="70"/>
-      <c r="D59" s="71">
-        <f>(SUM(D24:D57))</f>
-        <v>1557943.0299999998</v>
-      </c>
-      <c r="E59" s="25"/>
-      <c r="F59" s="25"/>
-    </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F58" s="25"/>
+    </row>
+    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A59" s="68"/>
+      <c r="B59" s="68"/>
+      <c r="C59" s="68"/>
+      <c r="D59" s="68"/>
+      <c r="F59" s="84"/>
+    </row>
+    <row r="60" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A60" s="68"/>
       <c r="B60" s="68"/>
       <c r="C60" s="68"/>
       <c r="D60" s="68"/>
-      <c r="F60" s="84"/>
-    </row>
-    <row r="61" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A61" s="68"/>
-      <c r="B61" s="68"/>
-      <c r="C61" s="68"/>
-      <c r="D61" s="68"/>
-    </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A62" s="128" t="s">
+    </row>
+    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A61" s="128" t="s">
         <v>27</v>
       </c>
-      <c r="B62" s="129"/>
-      <c r="C62" s="72"/>
-      <c r="D62" s="73"/>
-    </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B61" s="129"/>
+      <c r="C61" s="72"/>
+      <c r="D61" s="73"/>
+    </row>
+    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A62" s="148"/>
+      <c r="B62" s="149"/>
+      <c r="C62" s="61"/>
+      <c r="D62" s="59"/>
+    </row>
+    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63" s="148"/>
       <c r="B63" s="149"/>
       <c r="C63" s="61"/>
       <c r="D63" s="59"/>
     </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A64" s="148"/>
-      <c r="B64" s="149"/>
+    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A64" s="130"/>
+      <c r="B64" s="131"/>
       <c r="C64" s="61"/>
       <c r="D64" s="59"/>
     </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A65" s="130"/>
-      <c r="B65" s="131"/>
-      <c r="C65" s="61"/>
-      <c r="D65" s="59"/>
-    </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A66" s="132"/>
-      <c r="B66" s="133"/>
-      <c r="C66" s="134"/>
-      <c r="D66" s="31">
-        <f>SUM(C63:C65)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="67" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A65" s="132"/>
+      <c r="B65" s="133"/>
+      <c r="C65" s="134"/>
+      <c r="D65" s="31">
+        <f>SUM(C62:C64)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A66" s="68"/>
+      <c r="B66" s="68"/>
+      <c r="C66" s="68"/>
+    </row>
+    <row r="67" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A67" s="68"/>
       <c r="B67" s="68"/>
       <c r="C67" s="68"/>
     </row>
-    <row r="68" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A68" s="68"/>
-      <c r="B68" s="68"/>
-      <c r="C68" s="68"/>
-    </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A69" s="135" t="s">
+    <row r="68" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A68" s="135" t="s">
         <v>28</v>
       </c>
-      <c r="B69" s="135"/>
-      <c r="C69" s="136"/>
-      <c r="D69" s="91"/>
-    </row>
-    <row r="70" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A70" s="68"/>
-      <c r="B70" s="68"/>
-      <c r="C70" s="68"/>
-    </row>
-    <row r="71" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A71" s="126" t="s">
+      <c r="B68" s="135"/>
+      <c r="C68" s="136"/>
+      <c r="D68" s="91"/>
+    </row>
+    <row r="69" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A69" s="68"/>
+      <c r="B69" s="68"/>
+      <c r="C69" s="68"/>
+    </row>
+    <row r="70" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A70" s="126" t="s">
         <v>29</v>
       </c>
-      <c r="B71" s="127"/>
-      <c r="C71" s="70"/>
-      <c r="D71" s="38">
-        <f>D66+D69</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="72" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A72" s="68"/>
-      <c r="B72" s="68"/>
-      <c r="C72" s="68"/>
-    </row>
-    <row r="73" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B70" s="127"/>
+      <c r="C70" s="70"/>
+      <c r="D70" s="38">
+        <f>D65+D68</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A71" s="68"/>
+      <c r="B71" s="68"/>
+      <c r="C71" s="68"/>
+    </row>
+    <row r="72" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A72" s="137" t="s">
+        <v>20</v>
+      </c>
+      <c r="B72" s="138">
+        <f>D58</f>
+        <v>1471136.43</v>
+      </c>
+      <c r="C72" s="139"/>
+    </row>
+    <row r="73" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A73" s="137" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B73" s="138">
-        <f>D59</f>
-        <v>1557943.0299999998</v>
-      </c>
-      <c r="C73" s="139"/>
-    </row>
-    <row r="74" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <f>D58-D56</f>
+        <v>1471136.43</v>
+      </c>
+      <c r="C73" s="68"/>
+    </row>
+    <row r="74" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A74" s="137" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="B74" s="138">
-        <f>D59-D57</f>
-        <v>1557943.0299999998</v>
+        <f>D70-D68</f>
+        <v>0</v>
       </c>
       <c r="C74" s="68"/>
     </row>
-    <row r="75" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A75" s="137" t="s">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="B75" s="138">
-        <f>D71-D69</f>
+        <f>D70</f>
         <v>0</v>
       </c>
       <c r="C75" s="68"/>
     </row>
-    <row r="76" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A76" s="137" t="s">
-        <v>45</v>
-      </c>
-      <c r="B76" s="138">
-        <f>D71</f>
-        <v>0</v>
-      </c>
+    <row r="76" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A76" s="68"/>
+      <c r="B76" s="68"/>
       <c r="C76" s="68"/>
     </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A77" s="68"/>
       <c r="B77" s="68"/>
       <c r="C77" s="68"/>
     </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A78" s="68"/>
       <c r="B78" s="68"/>
       <c r="C78" s="68"/>
     </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A79" s="68"/>
-      <c r="B79" s="68"/>
+    <row r="79" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A79" s="140" t="s">
+        <v>39</v>
+      </c>
+      <c r="B79" s="141"/>
       <c r="C79" s="68"/>
     </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A80" s="140" t="s">
-        <v>39</v>
-      </c>
-      <c r="B80" s="141"/>
-      <c r="C80" s="68"/>
-    </row>
-    <row r="81" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A81" s="106" t="s">
-        <v>113</v>
-      </c>
-      <c r="B81" s="76">
+    <row r="80" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A80" s="106" t="s">
+        <v>112</v>
+      </c>
+      <c r="B80" s="76">
         <v>973176.49999999977</v>
       </c>
-      <c r="C81" s="139"/>
-      <c r="D81" s="25"/>
-    </row>
-    <row r="82" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C80" s="139"/>
+      <c r="D80" s="25"/>
+    </row>
+    <row r="81" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A81" s="107" t="s">
+        <v>48</v>
+      </c>
+      <c r="B81" s="23">
+        <f>PRORRATEO!G18</f>
+        <v>1220574.6600000001</v>
+      </c>
+    </row>
+    <row r="82" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" s="107" t="s">
-        <v>48</v>
-      </c>
-      <c r="B82" s="23">
-        <f>PRORRATEO!G18</f>
-        <v>1408850.6600000001</v>
-      </c>
-    </row>
-    <row r="83" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+        <v>47</v>
+      </c>
+      <c r="B82" s="62">
+        <f>B94</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" s="107" t="s">
-        <v>47</v>
-      </c>
-      <c r="B83" s="62">
-        <f>B95</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="84" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+        <v>116</v>
+      </c>
+      <c r="B83" s="86">
+        <v>-105000</v>
+      </c>
+    </row>
+    <row r="84" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" s="107" t="s">
-        <v>117</v>
+        <v>55</v>
       </c>
       <c r="B84" s="86">
-        <v>-105000</v>
-      </c>
-    </row>
-    <row r="85" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A85" s="107" t="s">
-        <v>55</v>
+        <v>-2873</v>
+      </c>
+    </row>
+    <row r="85" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A85" s="10" t="s">
+        <v>31</v>
       </c>
       <c r="B85" s="86">
-        <v>-2873</v>
-      </c>
-    </row>
-    <row r="86" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+        <f>-B73</f>
+        <v>-1471136.43</v>
+      </c>
+    </row>
+    <row r="86" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="B86" s="86">
-        <f>-B74</f>
-        <v>-1557943.0299999998</v>
-      </c>
-    </row>
-    <row r="87" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A87" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="B87" s="62">
-        <f>-(B75)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="88" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A88" s="108" t="s">
+      <c r="B86" s="62">
+        <f>-(B74)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A87" s="108" t="s">
         <v>8</v>
       </c>
-      <c r="B88" s="76">
-        <f>SUM(B81:B87)</f>
-        <v>716211.13000000035</v>
-      </c>
-      <c r="D88" s="25"/>
-    </row>
-    <row r="89" spans="1:12" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B89" s="24"/>
-      <c r="C89" s="25"/>
-    </row>
-    <row r="91" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A91" s="147" t="s">
+      <c r="B87" s="76">
+        <f>SUM(B80:B86)</f>
+        <v>614741.73000000021</v>
+      </c>
+      <c r="D87" s="25"/>
+    </row>
+    <row r="88" spans="1:12" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B88" s="24"/>
+      <c r="C88" s="25"/>
+    </row>
+    <row r="90" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A90" s="147" t="s">
         <v>38</v>
       </c>
+      <c r="B90" s="147"/>
+    </row>
+    <row r="91" spans="1:12" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A91" s="147"/>
       <c r="B91" s="147"/>
     </row>
-    <row r="92" spans="1:12" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A92" s="147"/>
-      <c r="B92" s="147"/>
-    </row>
-    <row r="93" spans="1:12" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:12" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A92" s="74"/>
+      <c r="B92" s="18"/>
+    </row>
+    <row r="93" spans="1:12" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93" s="74"/>
       <c r="B93" s="18"/>
     </row>
-    <row r="94" spans="1:12" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A94" s="74"/>
-      <c r="B94" s="18"/>
-    </row>
-    <row r="95" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A95" s="26" t="s">
+    <row r="94" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A94" s="26" t="s">
         <v>8</v>
       </c>
-      <c r="B95" s="75">
-        <f>SUM(B93:B94)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="96" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="L96" s="4"/>
+      <c r="B94" s="75">
+        <f>SUM(B92:B93)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="L95" s="4"/>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="9">
     <mergeCell ref="A4:B7"/>
     <mergeCell ref="A14:D17"/>
-    <mergeCell ref="A57:C57"/>
-    <mergeCell ref="A91:B92"/>
-    <mergeCell ref="A64:B64"/>
+    <mergeCell ref="A56:C56"/>
+    <mergeCell ref="A90:B91"/>
     <mergeCell ref="A63:B63"/>
+    <mergeCell ref="A62:B62"/>
     <mergeCell ref="B9:B11"/>
     <mergeCell ref="A34:B34"/>
     <mergeCell ref="A48:B48"/>
-    <mergeCell ref="A50:B50"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -2516,148 +2519,149 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:R25"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="4.5546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="7.33203125" customWidth="1"/>
-    <col min="3" max="3" width="10.109375" customWidth="1"/>
-    <col min="4" max="4" width="18.5546875" customWidth="1"/>
-    <col min="5" max="5" width="5.109375" customWidth="1"/>
-    <col min="6" max="6" width="14.109375" customWidth="1"/>
+    <col min="1" max="1" width="4.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="7.28515625" customWidth="1"/>
+    <col min="3" max="3" width="10.140625" customWidth="1"/>
+    <col min="4" max="4" width="18.5703125" customWidth="1"/>
+    <col min="5" max="5" width="5.140625" customWidth="1"/>
+    <col min="6" max="6" width="14.140625" customWidth="1"/>
     <col min="7" max="7" width="14" customWidth="1"/>
-    <col min="8" max="8" width="7.6640625" hidden="1" customWidth="1"/>
-    <col min="9" max="9" width="14.109375" customWidth="1"/>
-    <col min="10" max="10" width="14.33203125" customWidth="1"/>
-    <col min="11" max="11" width="14.109375" customWidth="1"/>
-    <col min="12" max="12" width="12.44140625" customWidth="1"/>
-    <col min="13" max="13" width="10.44140625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="15.33203125" customWidth="1"/>
-    <col min="15" max="15" width="14.109375" customWidth="1"/>
-    <col min="16" max="16" width="7.44140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="7.7109375" hidden="1" customWidth="1"/>
+    <col min="9" max="9" width="14.140625" customWidth="1"/>
+    <col min="10" max="10" width="14.28515625" customWidth="1"/>
+    <col min="11" max="11" width="14.140625" customWidth="1"/>
+    <col min="12" max="12" width="12.42578125" customWidth="1"/>
+    <col min="13" max="13" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="15.28515625" customWidth="1"/>
+    <col min="15" max="15" width="14.140625" customWidth="1"/>
+    <col min="16" max="16" width="7.42578125" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="12" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="13" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3"/>
-      <c r="B1" s="155" t="str">
+      <c r="B1" s="168" t="str">
         <f>RESUMEN!A4</f>
         <v>Banco: Santander
 C.U.I.T.   30-71774143-5
 CBU: 0720533020000000956840 ALIAS: BLONDA.LAGO.CORO
 Nº de cuenta: 533-009568/4</v>
       </c>
-      <c r="C1" s="156"/>
-      <c r="D1" s="156"/>
-      <c r="E1" s="157"/>
-      <c r="F1" s="155" t="s">
-        <v>114</v>
-      </c>
-      <c r="G1" s="156"/>
-      <c r="H1" s="156"/>
-      <c r="I1" s="157"/>
-      <c r="J1" s="151" t="s">
+      <c r="C1" s="169"/>
+      <c r="D1" s="169"/>
+      <c r="E1" s="170"/>
+      <c r="F1" s="168" t="s">
+        <v>113</v>
+      </c>
+      <c r="G1" s="169"/>
+      <c r="H1" s="169"/>
+      <c r="I1" s="170"/>
+      <c r="J1" s="164" t="s">
+        <v>109</v>
+      </c>
+      <c r="K1" s="165"/>
+      <c r="L1" s="114" t="s">
         <v>110</v>
-      </c>
-      <c r="K1" s="152"/>
-      <c r="L1" s="114" t="s">
-        <v>111</v>
       </c>
       <c r="M1" s="114"/>
       <c r="N1" s="116">
-        <v>1250000</v>
+        <f>1250000+(1250000*15%)</f>
+        <v>1437500</v>
       </c>
       <c r="O1" s="109"/>
       <c r="P1" s="9"/>
     </row>
-    <row r="2" spans="1:18" ht="43.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:18" ht="43.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="3"/>
-      <c r="B2" s="158"/>
-      <c r="C2" s="159"/>
-      <c r="D2" s="159"/>
-      <c r="E2" s="160"/>
-      <c r="F2" s="158"/>
-      <c r="G2" s="159"/>
-      <c r="H2" s="159"/>
-      <c r="I2" s="160"/>
-      <c r="J2" s="153"/>
-      <c r="K2" s="154"/>
+      <c r="B2" s="171"/>
+      <c r="C2" s="172"/>
+      <c r="D2" s="172"/>
+      <c r="E2" s="173"/>
+      <c r="F2" s="171"/>
+      <c r="G2" s="172"/>
+      <c r="H2" s="172"/>
+      <c r="I2" s="173"/>
+      <c r="J2" s="166"/>
+      <c r="K2" s="167"/>
       <c r="L2" s="115" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="M2" s="115"/>
       <c r="N2" s="95"/>
       <c r="O2" s="110"/>
     </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A3" s="161" t="s">
+    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A3" s="174" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="163" t="s">
+      <c r="B3" s="176" t="s">
         <v>58</v>
       </c>
-      <c r="C3" s="165" t="s">
+      <c r="C3" s="154" t="s">
         <v>59</v>
       </c>
-      <c r="D3" s="165" t="s">
+      <c r="D3" s="154" t="s">
         <v>5</v>
       </c>
-      <c r="E3" s="165" t="s">
+      <c r="E3" s="154" t="s">
         <v>17</v>
       </c>
-      <c r="F3" s="165" t="s">
+      <c r="F3" s="154" t="s">
         <v>46</v>
       </c>
-      <c r="G3" s="165" t="s">
+      <c r="G3" s="154" t="s">
         <v>6</v>
       </c>
-      <c r="H3" s="165" t="s">
+      <c r="H3" s="154" t="s">
         <v>35</v>
       </c>
-      <c r="I3" s="173" t="s">
+      <c r="I3" s="159" t="s">
         <v>36</v>
       </c>
-      <c r="J3" s="171" t="s">
+      <c r="J3" s="156" t="s">
         <v>34</v>
       </c>
-      <c r="K3" s="171" t="s">
+      <c r="K3" s="156" t="s">
         <v>7</v>
       </c>
-      <c r="L3" s="171" t="s">
+      <c r="L3" s="156" t="s">
         <v>33</v>
       </c>
-      <c r="M3" s="176" t="s">
+      <c r="M3" s="162" t="s">
         <v>44</v>
       </c>
       <c r="N3" s="34" t="s">
         <v>43</v>
       </c>
-      <c r="O3" s="167" t="s">
+      <c r="O3" s="151" t="s">
         <v>42</v>
       </c>
       <c r="R3" s="25"/>
     </row>
-    <row r="4" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="162"/>
-      <c r="B4" s="164"/>
-      <c r="C4" s="166"/>
-      <c r="D4" s="166"/>
-      <c r="E4" s="170"/>
-      <c r="F4" s="166"/>
-      <c r="G4" s="166"/>
-      <c r="H4" s="170"/>
-      <c r="I4" s="174"/>
-      <c r="J4" s="172"/>
-      <c r="K4" s="175"/>
-      <c r="L4" s="172"/>
-      <c r="M4" s="177"/>
+    <row r="4" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="175"/>
+      <c r="B4" s="177"/>
+      <c r="C4" s="158"/>
+      <c r="D4" s="158"/>
+      <c r="E4" s="155"/>
+      <c r="F4" s="158"/>
+      <c r="G4" s="158"/>
+      <c r="H4" s="155"/>
+      <c r="I4" s="160"/>
+      <c r="J4" s="157"/>
+      <c r="K4" s="161"/>
+      <c r="L4" s="157"/>
+      <c r="M4" s="163"/>
       <c r="N4" s="32" t="str">
         <f>RESUMEN!B9</f>
         <v>VTO 18/06</v>
       </c>
-      <c r="O4" s="168"/>
-    </row>
-    <row r="5" spans="1:18" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="O4" s="152"/>
+    </row>
+    <row r="5" spans="1:18" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>9</v>
       </c>
@@ -2674,15 +2678,15 @@
         <v>6.84</v>
       </c>
       <c r="F5" s="40">
-        <v>85500.01</v>
+        <v>82935.009999999995</v>
       </c>
       <c r="G5" s="41">
-        <v>88065</v>
+        <v>85423</v>
       </c>
       <c r="H5" s="42"/>
       <c r="I5" s="43">
         <f>F5-G5</f>
-        <v>-2564.9900000000052</v>
+        <v>-2487.9900000000052</v>
       </c>
       <c r="J5" s="43">
         <f>IF(I5&gt;0,I5*2.95%,0)</f>
@@ -2694,27 +2698,27 @@
       </c>
       <c r="L5" s="44">
         <f t="shared" ref="L5:L16" si="1">N$1*E5%</f>
-        <v>85500</v>
+        <v>98325</v>
       </c>
       <c r="M5" s="45">
         <v>0</v>
       </c>
       <c r="N5" s="46">
         <f>ROUND(I5+J5+K5+L5+M5,0) + P5</f>
-        <v>82935.009999999995</v>
+        <v>95837.01</v>
       </c>
       <c r="O5" s="47">
         <f t="shared" ref="O5:O16" si="2">ROUND(N5*3%,0) + N5</f>
-        <v>85423.01</v>
+        <v>98712.01</v>
       </c>
       <c r="P5" s="25">
         <v>0.01</v>
       </c>
       <c r="Q5" s="25" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="6" spans="1:18" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>9</v>
       </c>
@@ -2731,16 +2735,16 @@
         <v>7.79</v>
       </c>
       <c r="F6" s="40">
-        <v>197623.02</v>
+        <v>91230.02</v>
       </c>
       <c r="G6" s="41">
-        <f>105000+98552.02+2873</f>
-        <v>206425.02000000002</v>
+        <f>F6</f>
+        <v>91230.02</v>
       </c>
       <c r="H6" s="42"/>
       <c r="I6" s="97">
         <f t="shared" ref="I6:I16" si="3">F6-G6</f>
-        <v>-8802.0000000000291</v>
+        <v>0</v>
       </c>
       <c r="J6" s="97">
         <f t="shared" ref="J6:J16" si="4">IF(I6&gt;0,I6*2.95%,0)</f>
@@ -2752,28 +2756,28 @@
       </c>
       <c r="L6" s="98">
         <f t="shared" si="1"/>
-        <v>97375</v>
+        <v>111981.25</v>
       </c>
       <c r="M6" s="99">
         <v>0</v>
       </c>
       <c r="N6" s="100">
         <f t="shared" ref="N6:N16" si="5">ROUND(SUM(I6:M6),0) + P6</f>
-        <v>88573.02</v>
+        <v>111981.02</v>
       </c>
       <c r="O6" s="101">
         <f t="shared" si="2"/>
-        <v>91230.02</v>
+        <v>115340.02</v>
       </c>
       <c r="P6" s="25">
         <f>P5+0.01</f>
         <v>0.02</v>
       </c>
       <c r="Q6" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="7" spans="1:18" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="117" t="s">
         <v>10</v>
       </c>
@@ -2811,29 +2815,29 @@
       </c>
       <c r="L7" s="44">
         <f t="shared" si="1"/>
-        <v>84375</v>
+        <v>97031.25</v>
       </c>
       <c r="M7" s="45">
         <v>0</v>
       </c>
       <c r="N7" s="46">
         <f t="shared" si="5"/>
-        <v>84375.03</v>
+        <v>97031.03</v>
       </c>
       <c r="O7" s="47">
         <f t="shared" si="2"/>
-        <v>86906.03</v>
+        <v>99942.03</v>
       </c>
       <c r="P7" s="25">
         <f t="shared" ref="P7:P16" si="6">P6+0.01</f>
         <v>0.03</v>
       </c>
       <c r="Q7" t="s">
-        <v>107</v>
+        <v>133</v>
       </c>
       <c r="R7" s="25"/>
     </row>
-    <row r="8" spans="1:18" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:18" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>10</v>
       </c>
@@ -2871,29 +2875,29 @@
       </c>
       <c r="L8" s="44">
         <f t="shared" si="1"/>
-        <v>92625</v>
+        <v>106518.75</v>
       </c>
       <c r="M8" s="45">
         <v>0</v>
       </c>
       <c r="N8" s="46">
         <f t="shared" si="5"/>
-        <v>92625.04</v>
+        <v>106519.03999999999</v>
       </c>
       <c r="O8" s="47">
         <f t="shared" si="2"/>
-        <v>95404.04</v>
+        <v>109715.04</v>
       </c>
       <c r="P8" s="25">
         <f t="shared" si="6"/>
         <v>0.04</v>
       </c>
       <c r="Q8" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="R8" s="25"/>
     </row>
-    <row r="9" spans="1:18" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:18" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="117" t="s">
         <v>11</v>
       </c>
@@ -2913,16 +2917,16 @@
         <v>100000.05</v>
       </c>
       <c r="G9" s="41">
-        <v>100000</v>
+        <v>101000</v>
       </c>
       <c r="H9" s="42"/>
       <c r="I9" s="43">
         <f t="shared" si="3"/>
-        <v>5.0000000002910383E-2</v>
+        <v>-999.94999999999709</v>
       </c>
       <c r="J9" s="43">
         <f t="shared" si="4"/>
-        <v>1.4750000000858564E-3</v>
+        <v>0</v>
       </c>
       <c r="K9" s="44">
         <f t="shared" si="0"/>
@@ -2930,28 +2934,28 @@
       </c>
       <c r="L9" s="44">
         <f t="shared" si="1"/>
-        <v>100000</v>
+        <v>115000</v>
       </c>
       <c r="M9" s="45">
         <v>0</v>
       </c>
       <c r="N9" s="46">
         <f t="shared" si="5"/>
-        <v>100000.05</v>
+        <v>114000.05</v>
       </c>
       <c r="O9" s="47">
         <f t="shared" si="2"/>
-        <v>103000.05</v>
+        <v>117420.05</v>
       </c>
       <c r="P9" s="25">
         <f t="shared" si="6"/>
         <v>0.05</v>
       </c>
       <c r="Q9" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="10" spans="1:18" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>11</v>
       </c>
@@ -2968,19 +2972,19 @@
         <v>6.97</v>
       </c>
       <c r="F10" s="40">
-        <v>158969.06</v>
+        <v>141665.06</v>
       </c>
       <c r="G10" s="41">
-        <v>110000</v>
+        <v>90000</v>
       </c>
       <c r="H10" s="42"/>
       <c r="I10" s="43">
         <f t="shared" si="3"/>
-        <v>48969.06</v>
+        <v>51665.06</v>
       </c>
       <c r="J10" s="43">
         <f t="shared" si="4"/>
-        <v>1444.58727</v>
+        <v>1524.1192700000001</v>
       </c>
       <c r="K10" s="44">
         <f t="shared" si="0"/>
@@ -2988,18 +2992,18 @@
       </c>
       <c r="L10" s="44">
         <f t="shared" si="1"/>
-        <v>87125</v>
+        <v>100193.75</v>
       </c>
       <c r="M10" s="45">
         <v>0</v>
       </c>
       <c r="N10" s="46">
         <f t="shared" si="5"/>
-        <v>137539.06</v>
+        <v>153383.06</v>
       </c>
       <c r="O10" s="47">
         <f t="shared" si="2"/>
-        <v>141665.06</v>
+        <v>157984.06</v>
       </c>
       <c r="P10" s="25">
         <f t="shared" si="6"/>
@@ -3008,7 +3012,7 @@
       <c r="Q10" s="84"/>
       <c r="R10" s="83"/>
     </row>
-    <row r="11" spans="1:18" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:18" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>12</v>
       </c>
@@ -3046,18 +3050,18 @@
       </c>
       <c r="L11" s="44">
         <f t="shared" si="1"/>
-        <v>84375</v>
+        <v>97031.25</v>
       </c>
       <c r="M11" s="45">
         <v>0</v>
       </c>
       <c r="N11" s="46">
         <f t="shared" si="5"/>
-        <v>84375.07</v>
+        <v>97031.07</v>
       </c>
       <c r="O11" s="47">
         <f t="shared" si="2"/>
-        <v>86906.07</v>
+        <v>99942.07</v>
       </c>
       <c r="P11" s="25">
         <f t="shared" si="6"/>
@@ -3067,7 +3071,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="12" spans="1:18" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:18" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>12</v>
       </c>
@@ -3105,25 +3109,25 @@
       </c>
       <c r="L12" s="44">
         <f t="shared" si="1"/>
-        <v>97375</v>
+        <v>111981.25</v>
       </c>
       <c r="M12" s="45">
         <v>0</v>
       </c>
       <c r="N12" s="46">
         <f t="shared" si="5"/>
-        <v>97375.08</v>
+        <v>111981.08</v>
       </c>
       <c r="O12" s="47">
         <f t="shared" si="2"/>
-        <v>100296.08</v>
+        <v>115340.08</v>
       </c>
       <c r="P12" s="25">
         <f t="shared" si="6"/>
         <v>0.08</v>
       </c>
     </row>
-    <row r="13" spans="1:18" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:18" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>13</v>
       </c>
@@ -3161,28 +3165,28 @@
       </c>
       <c r="L13" s="44">
         <f t="shared" si="1"/>
-        <v>95250</v>
+        <v>109537.5</v>
       </c>
       <c r="M13" s="45">
         <v>0</v>
       </c>
       <c r="N13" s="46">
         <f t="shared" si="5"/>
-        <v>95250.09</v>
+        <v>109538.09</v>
       </c>
       <c r="O13" s="47">
         <f t="shared" si="2"/>
-        <v>98108.09</v>
+        <v>112824.09</v>
       </c>
       <c r="P13" s="25">
         <f t="shared" si="6"/>
         <v>0.09</v>
       </c>
       <c r="Q13" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="14" spans="1:18" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>13</v>
       </c>
@@ -3193,21 +3197,22 @@
         <v>88</v>
       </c>
       <c r="D14" s="102" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E14" s="105">
         <v>6.97</v>
       </c>
       <c r="F14" s="40">
-        <v>87125.1</v>
+        <v>87046.1</v>
       </c>
       <c r="G14" s="41">
-        <v>89739.1</v>
+        <f>60000+27046.1</f>
+        <v>87046.1</v>
       </c>
       <c r="H14" s="42"/>
       <c r="I14" s="43">
         <f t="shared" si="3"/>
-        <v>-2614</v>
+        <v>0</v>
       </c>
       <c r="J14" s="43">
         <f t="shared" si="4"/>
@@ -3219,25 +3224,25 @@
       </c>
       <c r="L14" s="44">
         <f t="shared" si="1"/>
-        <v>87125</v>
+        <v>100193.75</v>
       </c>
       <c r="M14" s="45">
         <v>0</v>
       </c>
       <c r="N14" s="46">
         <f t="shared" si="5"/>
-        <v>84511.1</v>
+        <v>100194.1</v>
       </c>
       <c r="O14" s="47">
         <f t="shared" si="2"/>
-        <v>87046.1</v>
+        <v>103200.1</v>
       </c>
       <c r="P14" s="25">
         <f t="shared" si="6"/>
         <v>9.9999999999999992E-2</v>
       </c>
     </row>
-    <row r="15" spans="1:18" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:18" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
         <v>14</v>
       </c>
@@ -3254,15 +3259,16 @@
         <v>14.01</v>
       </c>
       <c r="F15" s="40">
-        <v>169871.11</v>
+        <v>148125.10999999999</v>
       </c>
       <c r="G15" s="41">
-        <v>196871.11</v>
+        <f>F15</f>
+        <v>148125.10999999999</v>
       </c>
       <c r="H15" s="42"/>
       <c r="I15" s="43">
         <f t="shared" si="3"/>
-        <v>-27000</v>
+        <v>0</v>
       </c>
       <c r="J15" s="43">
         <f t="shared" si="4"/>
@@ -3274,28 +3280,28 @@
       </c>
       <c r="L15" s="44">
         <f t="shared" si="1"/>
-        <v>175125</v>
+        <v>201393.75</v>
       </c>
       <c r="M15" s="45">
         <v>0</v>
       </c>
       <c r="N15" s="46">
         <f t="shared" si="5"/>
-        <v>148125.10999999999</v>
+        <v>201394.11</v>
       </c>
       <c r="O15" s="47">
         <f t="shared" si="2"/>
-        <v>152569.10999999999</v>
+        <v>207436.11</v>
       </c>
       <c r="P15" s="25">
         <f t="shared" si="6"/>
         <v>0.10999999999999999</v>
       </c>
       <c r="Q15" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="16" spans="1:18" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
         <v>14</v>
       </c>
@@ -3333,18 +3339,18 @@
       </c>
       <c r="L16" s="44">
         <f t="shared" si="1"/>
-        <v>163750</v>
+        <v>188312.5</v>
       </c>
       <c r="M16" s="45">
         <v>0</v>
       </c>
       <c r="N16" s="46">
         <f t="shared" si="5"/>
-        <v>163750.12</v>
+        <v>188313.12</v>
       </c>
       <c r="O16" s="47">
         <f t="shared" si="2"/>
-        <v>168663.12</v>
+        <v>193962.12</v>
       </c>
       <c r="P16" s="25">
         <f t="shared" si="6"/>
@@ -3354,7 +3360,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="17" spans="1:16" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:16" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
         <v>16</v>
       </c>
@@ -3374,7 +3380,7 @@
       <c r="O17" s="47"/>
       <c r="P17" s="25"/>
     </row>
-    <row r="18" spans="1:16" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:16" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B18" s="48"/>
       <c r="C18" s="49"/>
       <c r="D18" s="50"/>
@@ -3384,11 +3390,11 @@
       </c>
       <c r="F18" s="28">
         <f>SUM(F5:F17)</f>
-        <v>1416838.7800000003</v>
+        <v>1268751.7799999998</v>
       </c>
       <c r="G18" s="33">
         <f>SUM(G5:G17)</f>
-        <v>1408850.6600000001</v>
+        <v>1220574.6600000001</v>
       </c>
       <c r="H18" s="33">
         <f>SUM(H5:H17)</f>
@@ -3402,7 +3408,7 @@
       </c>
       <c r="L18" s="33">
         <f>SUM(L5:L17)</f>
-        <v>1250000</v>
+        <v>1437500</v>
       </c>
       <c r="M18" s="33">
         <f>SUM(M5:M17)</f>
@@ -3410,98 +3416,105 @@
       </c>
       <c r="N18" s="52">
         <f>SUM(N5:N17)</f>
-        <v>1259433.7799999998</v>
+        <v>1487202.7800000003</v>
       </c>
       <c r="O18" s="52">
         <f>SUM(O5:O17)</f>
-        <v>1297216.7799999998</v>
-      </c>
-    </row>
-    <row r="19" spans="1:16" x14ac:dyDescent="0.3">
+        <v>1531817.7800000003</v>
+      </c>
+    </row>
+    <row r="19" spans="1:16" x14ac:dyDescent="0.25">
       <c r="D19" s="27"/>
     </row>
-    <row r="20" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="D20" s="169" t="s">
+    <row r="20" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="D20" s="153" t="s">
         <v>56</v>
       </c>
-      <c r="E20" s="169"/>
-      <c r="F20" s="169"/>
-      <c r="G20" s="169"/>
-      <c r="H20" s="169"/>
-      <c r="I20" s="169"/>
-      <c r="J20" s="169"/>
-      <c r="K20" s="169"/>
-      <c r="L20" s="169"/>
-      <c r="M20" s="169"/>
-      <c r="N20" s="169"/>
-    </row>
-    <row r="21" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="D21" s="169"/>
-      <c r="E21" s="169"/>
-      <c r="F21" s="169"/>
-      <c r="G21" s="169"/>
-      <c r="H21" s="169"/>
-      <c r="I21" s="169"/>
-      <c r="J21" s="169"/>
-      <c r="K21" s="169"/>
-      <c r="L21" s="169"/>
-      <c r="M21" s="169"/>
-      <c r="N21" s="169"/>
-    </row>
-    <row r="22" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="D22" s="169"/>
-      <c r="E22" s="169"/>
-      <c r="F22" s="169"/>
-      <c r="G22" s="169"/>
-      <c r="H22" s="169"/>
-      <c r="I22" s="169"/>
-      <c r="J22" s="169"/>
-      <c r="K22" s="169"/>
-      <c r="L22" s="169"/>
-      <c r="M22" s="169"/>
-      <c r="N22" s="169"/>
-    </row>
-    <row r="23" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="D23" s="169"/>
-      <c r="E23" s="169"/>
-      <c r="F23" s="169"/>
-      <c r="G23" s="169"/>
-      <c r="H23" s="169"/>
-      <c r="I23" s="169"/>
-      <c r="J23" s="169"/>
-      <c r="K23" s="169"/>
-      <c r="L23" s="169"/>
-      <c r="M23" s="169"/>
-      <c r="N23" s="169"/>
-    </row>
-    <row r="24" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="D24" s="169"/>
-      <c r="E24" s="169"/>
-      <c r="F24" s="169"/>
-      <c r="G24" s="169"/>
-      <c r="H24" s="169"/>
-      <c r="I24" s="169"/>
-      <c r="J24" s="169"/>
-      <c r="K24" s="169"/>
-      <c r="L24" s="169"/>
-      <c r="M24" s="169"/>
-      <c r="N24" s="169"/>
-    </row>
-    <row r="25" spans="1:16" ht="4.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D25" s="169"/>
-      <c r="E25" s="169"/>
-      <c r="F25" s="169"/>
-      <c r="G25" s="169"/>
-      <c r="H25" s="169"/>
-      <c r="I25" s="169"/>
-      <c r="J25" s="169"/>
-      <c r="K25" s="169"/>
-      <c r="L25" s="169"/>
-      <c r="M25" s="169"/>
-      <c r="N25" s="169"/>
+      <c r="E20" s="153"/>
+      <c r="F20" s="153"/>
+      <c r="G20" s="153"/>
+      <c r="H20" s="153"/>
+      <c r="I20" s="153"/>
+      <c r="J20" s="153"/>
+      <c r="K20" s="153"/>
+      <c r="L20" s="153"/>
+      <c r="M20" s="153"/>
+      <c r="N20" s="153"/>
+    </row>
+    <row r="21" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="D21" s="153"/>
+      <c r="E21" s="153"/>
+      <c r="F21" s="153"/>
+      <c r="G21" s="153"/>
+      <c r="H21" s="153"/>
+      <c r="I21" s="153"/>
+      <c r="J21" s="153"/>
+      <c r="K21" s="153"/>
+      <c r="L21" s="153"/>
+      <c r="M21" s="153"/>
+      <c r="N21" s="153"/>
+    </row>
+    <row r="22" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="D22" s="153"/>
+      <c r="E22" s="153"/>
+      <c r="F22" s="153"/>
+      <c r="G22" s="153"/>
+      <c r="H22" s="153"/>
+      <c r="I22" s="153"/>
+      <c r="J22" s="153"/>
+      <c r="K22" s="153"/>
+      <c r="L22" s="153"/>
+      <c r="M22" s="153"/>
+      <c r="N22" s="153"/>
+    </row>
+    <row r="23" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="D23" s="153"/>
+      <c r="E23" s="153"/>
+      <c r="F23" s="153"/>
+      <c r="G23" s="153"/>
+      <c r="H23" s="153"/>
+      <c r="I23" s="153"/>
+      <c r="J23" s="153"/>
+      <c r="K23" s="153"/>
+      <c r="L23" s="153"/>
+      <c r="M23" s="153"/>
+      <c r="N23" s="153"/>
+    </row>
+    <row r="24" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="D24" s="153"/>
+      <c r="E24" s="153"/>
+      <c r="F24" s="153"/>
+      <c r="G24" s="153"/>
+      <c r="H24" s="153"/>
+      <c r="I24" s="153"/>
+      <c r="J24" s="153"/>
+      <c r="K24" s="153"/>
+      <c r="L24" s="153"/>
+      <c r="M24" s="153"/>
+      <c r="N24" s="153"/>
+    </row>
+    <row r="25" spans="1:16" ht="4.9000000000000004" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D25" s="153"/>
+      <c r="E25" s="153"/>
+      <c r="F25" s="153"/>
+      <c r="G25" s="153"/>
+      <c r="H25" s="153"/>
+      <c r="I25" s="153"/>
+      <c r="J25" s="153"/>
+      <c r="K25" s="153"/>
+      <c r="L25" s="153"/>
+      <c r="M25" s="153"/>
+      <c r="N25" s="153"/>
     </row>
   </sheetData>
   <mergeCells count="18">
+    <mergeCell ref="J1:K2"/>
+    <mergeCell ref="B1:E2"/>
+    <mergeCell ref="F1:I2"/>
+    <mergeCell ref="A3:A4"/>
+    <mergeCell ref="B3:B4"/>
+    <mergeCell ref="C3:C4"/>
+    <mergeCell ref="D3:D4"/>
     <mergeCell ref="O3:O4"/>
     <mergeCell ref="D20:N25"/>
     <mergeCell ref="H3:H4"/>
@@ -3513,13 +3526,6 @@
     <mergeCell ref="L3:L4"/>
     <mergeCell ref="M3:M4"/>
     <mergeCell ref="E3:E4"/>
-    <mergeCell ref="J1:K2"/>
-    <mergeCell ref="B1:E2"/>
-    <mergeCell ref="F1:I2"/>
-    <mergeCell ref="A3:A4"/>
-    <mergeCell ref="B3:B4"/>
-    <mergeCell ref="C3:C4"/>
-    <mergeCell ref="D3:D4"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="3" orientation="landscape" r:id="rId1"/>
@@ -3529,9 +3535,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B3E9F1C8-DABE-4F17-BF70-F15A1A832000}">
   <dimension ref="C4"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="4" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C4" s="83"/>
     </row>
   </sheetData>

--- a/2026/CABRERA/Mayo/Mayo CABRERA.xlsx
+++ b/2026/CABRERA/Mayo/Mayo CABRERA.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistemax\Desktop\rc-consorcio2025\2026\CABRERA\Mayo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60C36BD2-DC8B-4289-9305-FC797002A6FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A137D91A-70EE-4D97-AC77-C5EDB43A699E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="793" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="793" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RESUMEN" sheetId="1" r:id="rId1"/>
@@ -19,7 +19,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="1">PRORRATEO!$A$1:$O$26</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$D$95</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$D$93</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
   <extLst>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="134">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="133">
   <si>
     <t>TOTAL SUELDO</t>
   </si>
@@ -196,9 +196,6 @@
   </si>
   <si>
     <t>Sindicatos :  Fatherhy</t>
-  </si>
-  <si>
-    <t>Punitorios mal cobrados</t>
   </si>
   <si>
     <t>SI EN LA COLUMNA LLAMADA DEUDA O SALDO A FAVOR FIGURA UN NUMERO EN NEGATIVO SIGNIFICA QUE LA UF POSEE DINERO A FAVOR (ES DECIR PAGO DE MAS)</t>
@@ -372,9 +369,6 @@
     <t>EXTRAORDINARIOS:</t>
   </si>
   <si>
-    <t>Saldo anterior REAL según banco</t>
-  </si>
-  <si>
     <t>MEDIOS DE CONTACTOS: cabrera140rc@gmail.com  - INFORMAR CUALQUIER TIPO DE PAGO POR ALLI</t>
   </si>
   <si>
@@ -384,9 +378,6 @@
     <t xml:space="preserve">franco attolino </t>
   </si>
   <si>
-    <t>Transferencia ya identificada mes anterior</t>
-  </si>
-  <si>
     <t>Facundo Guarinello</t>
   </si>
   <si>
@@ -405,9 +396,6 @@
     <t>Lucas damian rivero</t>
   </si>
   <si>
-    <t>Transf 08/04</t>
-  </si>
-  <si>
     <t>Abdon alberto</t>
   </si>
   <si>
@@ -436,6 +424,15 @@
   </si>
   <si>
     <t>Ezequiel Mazzio</t>
+  </si>
+  <si>
+    <t>Transf 26/05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Saldo anterior </t>
+  </si>
+  <si>
+    <t>Hace unos meses venimos arrastrando una diferencia de caja de $51.266 (Tenemos mas en el banco de lo que dice el excel)- Revisar</t>
   </si>
 </sst>
 </file>
@@ -1260,6 +1257,9 @@
     <xf numFmtId="44" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="44" fontId="8" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="8" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -1287,6 +1287,54 @@
     <xf numFmtId="0" fontId="15" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="13" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1296,9 +1344,6 @@
     <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1308,9 +1353,6 @@
     <xf numFmtId="0" fontId="11" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="12" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1326,52 +1368,9 @@
     <xf numFmtId="0" fontId="11" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="8" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="4" fillId="9" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Moneda" xfId="1" builtinId="4"/>
@@ -1760,7 +1759,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L95"/>
+  <dimension ref="A1:L93"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="37.5703125" customWidth="1"/>
@@ -1784,7 +1783,7 @@
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="78" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B2" s="78"/>
       <c r="C2" s="78"/>
@@ -1792,85 +1791,85 @@
     </row>
     <row r="3" spans="1:8" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="78" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B3" s="78"/>
       <c r="C3" s="78"/>
       <c r="D3" s="78"/>
     </row>
     <row r="4" spans="1:8" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="142" t="s">
-        <v>108</v>
-      </c>
-      <c r="B4" s="142"/>
+      <c r="A4" s="143" t="s">
+        <v>107</v>
+      </c>
+      <c r="B4" s="143"/>
       <c r="C4" s="79"/>
       <c r="D4" s="79"/>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A5" s="142"/>
-      <c r="B5" s="142"/>
+      <c r="A5" s="143"/>
+      <c r="B5" s="143"/>
       <c r="C5" s="79"/>
       <c r="D5" s="79"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A6" s="142"/>
-      <c r="B6" s="142"/>
+      <c r="A6" s="143"/>
+      <c r="B6" s="143"/>
       <c r="C6" s="79"/>
       <c r="D6" s="79"/>
     </row>
     <row r="7" spans="1:8" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="142"/>
-      <c r="B7" s="142"/>
+      <c r="A7" s="143"/>
+      <c r="B7" s="143"/>
       <c r="C7" s="79"/>
       <c r="D7" s="79"/>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B9" s="150" t="s">
-        <v>125</v>
+      <c r="B9" s="151" t="s">
+        <v>121</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B10" s="150"/>
+      <c r="B10" s="151"/>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B11" s="150"/>
+      <c r="B11" s="151"/>
     </row>
     <row r="13" spans="1:8" ht="14.45" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="F13" t="s">
+        <v>98</v>
+      </c>
+      <c r="G13" t="s">
         <v>99</v>
       </c>
-      <c r="G13" t="s">
+      <c r="H13" t="s">
         <v>100</v>
       </c>
-      <c r="H13" t="s">
-        <v>101</v>
-      </c>
     </row>
     <row r="14" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="143" t="s">
+      <c r="A14" s="144" t="s">
         <v>49</v>
       </c>
-      <c r="B14" s="143"/>
-      <c r="C14" s="143"/>
-      <c r="D14" s="143"/>
+      <c r="B14" s="144"/>
+      <c r="C14" s="144"/>
+      <c r="D14" s="144"/>
     </row>
     <row r="15" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="143"/>
-      <c r="B15" s="143"/>
-      <c r="C15" s="143"/>
-      <c r="D15" s="143"/>
+      <c r="A15" s="144"/>
+      <c r="B15" s="144"/>
+      <c r="C15" s="144"/>
+      <c r="D15" s="144"/>
     </row>
     <row r="16" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="143"/>
-      <c r="B16" s="143"/>
-      <c r="C16" s="143"/>
-      <c r="D16" s="143"/>
+      <c r="A16" s="144"/>
+      <c r="B16" s="144"/>
+      <c r="C16" s="144"/>
+      <c r="D16" s="144"/>
     </row>
     <row r="17" spans="1:7" ht="53.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="143"/>
-      <c r="B17" s="143"/>
-      <c r="C17" s="143"/>
-      <c r="D17" s="143"/>
+      <c r="A17" s="144"/>
+      <c r="B17" s="144"/>
+      <c r="C17" s="144"/>
+      <c r="D17" s="144"/>
     </row>
     <row r="18" spans="1:7" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="19" spans="1:7" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -1895,14 +1894,14 @@
     </row>
     <row r="23" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B23" s="2"/>
       <c r="C23" s="92">
         <v>475000</v>
       </c>
       <c r="D23" s="85" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
     </row>
     <row r="24" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
@@ -1964,14 +1963,14 @@
     </row>
     <row r="31" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="118" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="B31" s="119"/>
-      <c r="C31" s="178">
+      <c r="C31" s="142">
         <v>102000</v>
       </c>
       <c r="D31" s="90" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="G31" s="9"/>
     </row>
@@ -1995,15 +1994,15 @@
       <c r="D33" s="37"/>
     </row>
     <row r="34" spans="1:6" s="22" customFormat="1" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="148" t="s">
-        <v>120</v>
-      </c>
-      <c r="B34" s="149"/>
+      <c r="A34" s="149" t="s">
+        <v>117</v>
+      </c>
+      <c r="B34" s="150"/>
       <c r="C34" s="112">
         <v>87769</v>
       </c>
       <c r="D34" s="89" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
     </row>
     <row r="35" spans="1:6" ht="14.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -2030,7 +2029,7 @@
         <v>51</v>
       </c>
       <c r="B37" s="53" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="C37" s="113"/>
       <c r="D37" s="89"/>
@@ -2041,7 +2040,7 @@
         <v>52</v>
       </c>
       <c r="B38" s="53" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="C38" s="94"/>
       <c r="D38" s="89"/>
@@ -2051,7 +2050,7 @@
         <v>53</v>
       </c>
       <c r="B39" s="53" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="C39" s="94"/>
       <c r="D39" s="89"/>
@@ -2061,7 +2060,7 @@
         <v>54</v>
       </c>
       <c r="B40" s="53" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="C40" s="94"/>
       <c r="D40" s="88"/>
@@ -2087,38 +2086,38 @@
     </row>
     <row r="43" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="68" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B43" s="53"/>
       <c r="C43" s="94">
         <v>96924.479999999996</v>
       </c>
       <c r="D43" s="87" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
     </row>
     <row r="44" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="53" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B44" s="53"/>
       <c r="C44" s="94">
         <v>205492.85</v>
       </c>
       <c r="D44" s="87" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
     </row>
     <row r="45" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="53" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B45" s="53"/>
       <c r="C45" s="94">
         <v>324588.2</v>
       </c>
       <c r="D45" s="87" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
     </row>
     <row r="46" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -2141,15 +2140,15 @@
       <c r="D47" s="60"/>
     </row>
     <row r="48" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="148" t="s">
-        <v>121</v>
-      </c>
-      <c r="B48" s="149"/>
+      <c r="A48" s="149" t="s">
+        <v>118</v>
+      </c>
+      <c r="B48" s="150"/>
       <c r="C48" s="94">
         <v>73200</v>
       </c>
       <c r="D48" s="85" t="s">
-        <v>123</v>
+        <v>130</v>
       </c>
     </row>
     <row r="49" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -2180,7 +2179,7 @@
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" s="53" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B52" s="53"/>
       <c r="C52" s="94">
@@ -2190,11 +2189,11 @@
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" s="53" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B53" s="53"/>
-      <c r="C53" s="179">
-        <v>37161.9</v>
+      <c r="C53" s="94">
+        <v>37109.67</v>
       </c>
       <c r="D53" s="62"/>
     </row>
@@ -2206,7 +2205,7 @@
       <c r="C54" s="65"/>
       <c r="D54" s="57">
         <f>SUM(C52:C53)</f>
-        <v>106161.9</v>
+        <v>106109.67</v>
       </c>
     </row>
     <row r="55" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -2216,11 +2215,11 @@
       <c r="D55" s="66"/>
     </row>
     <row r="56" spans="1:6" ht="22.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A56" s="144" t="s">
-        <v>118</v>
-      </c>
-      <c r="B56" s="145"/>
-      <c r="C56" s="146"/>
+      <c r="A56" s="145" t="s">
+        <v>115</v>
+      </c>
+      <c r="B56" s="146"/>
+      <c r="C56" s="147"/>
       <c r="D56" s="67"/>
     </row>
     <row r="57" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -2238,7 +2237,7 @@
       <c r="C58" s="70"/>
       <c r="D58" s="71">
         <f>(SUM(D24:D56))</f>
-        <v>1471136.43</v>
+        <v>1471084.2</v>
       </c>
       <c r="E58" s="25"/>
       <c r="F58" s="25"/>
@@ -2265,14 +2264,14 @@
       <c r="D61" s="73"/>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A62" s="148"/>
-      <c r="B62" s="149"/>
+      <c r="A62" s="149"/>
+      <c r="B62" s="150"/>
       <c r="C62" s="61"/>
       <c r="D62" s="59"/>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A63" s="148"/>
-      <c r="B63" s="149"/>
+      <c r="A63" s="149"/>
+      <c r="B63" s="150"/>
       <c r="C63" s="61"/>
       <c r="D63" s="59"/>
     </row>
@@ -2282,7 +2281,7 @@
       <c r="C64" s="61"/>
       <c r="D64" s="59"/>
     </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A65" s="132"/>
       <c r="B65" s="133"/>
       <c r="C65" s="134"/>
@@ -2291,17 +2290,17 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="68"/>
       <c r="B66" s="68"/>
       <c r="C66" s="68"/>
     </row>
-    <row r="67" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A67" s="68"/>
       <c r="B67" s="68"/>
       <c r="C67" s="68"/>
     </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A68" s="135" t="s">
         <v>28</v>
       </c>
@@ -2309,12 +2308,12 @@
       <c r="C68" s="136"/>
       <c r="D68" s="91"/>
     </row>
-    <row r="69" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A69" s="68"/>
       <c r="B69" s="68"/>
       <c r="C69" s="68"/>
     </row>
-    <row r="70" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A70" s="126" t="s">
         <v>29</v>
       </c>
@@ -2325,32 +2324,32 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A71" s="68"/>
       <c r="B71" s="68"/>
       <c r="C71" s="68"/>
     </row>
-    <row r="72" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A72" s="137" t="s">
         <v>20</v>
       </c>
       <c r="B72" s="138">
         <f>D58</f>
-        <v>1471136.43</v>
+        <v>1471084.2</v>
       </c>
       <c r="C72" s="139"/>
     </row>
-    <row r="73" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A73" s="137" t="s">
         <v>21</v>
       </c>
       <c r="B73" s="138">
         <f>D58-D56</f>
-        <v>1471136.43</v>
+        <v>1471084.2</v>
       </c>
       <c r="C73" s="68"/>
     </row>
-    <row r="74" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A74" s="137" t="s">
         <v>30</v>
       </c>
@@ -2360,7 +2359,7 @@
       </c>
       <c r="C74" s="68"/>
     </row>
-    <row r="75" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A75" s="137" t="s">
         <v>45</v>
       </c>
@@ -2370,37 +2369,40 @@
       </c>
       <c r="C75" s="68"/>
     </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A76" s="68"/>
       <c r="B76" s="68"/>
       <c r="C76" s="68"/>
     </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A77" s="68"/>
       <c r="B77" s="68"/>
       <c r="C77" s="68"/>
     </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A78" s="68"/>
       <c r="B78" s="68"/>
       <c r="C78" s="68"/>
     </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A79" s="140" t="s">
         <v>39</v>
       </c>
       <c r="B79" s="141"/>
       <c r="C79" s="68"/>
     </row>
-    <row r="80" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" s="106" t="s">
-        <v>112</v>
+        <v>131</v>
       </c>
       <c r="B80" s="76">
-        <v>973176.49999999977</v>
+        <v>733575.9600000002</v>
       </c>
       <c r="C80" s="139"/>
       <c r="D80" s="25"/>
+      <c r="G80" s="179" t="s">
+        <v>132</v>
+      </c>
     </row>
     <row r="81" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="107" t="s">
@@ -2410,100 +2412,91 @@
         <f>PRORRATEO!G18</f>
         <v>1220574.6600000001</v>
       </c>
+      <c r="G81" s="179"/>
     </row>
     <row r="82" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" s="107" t="s">
         <v>47</v>
       </c>
       <c r="B82" s="62">
-        <f>B94</f>
-        <v>0</v>
-      </c>
+        <f>B92</f>
+        <v>0</v>
+      </c>
+      <c r="G82" s="179"/>
     </row>
     <row r="83" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A83" s="107" t="s">
-        <v>116</v>
+      <c r="A83" s="10" t="s">
+        <v>31</v>
       </c>
       <c r="B83" s="86">
-        <v>-105000</v>
-      </c>
+        <f>-B73</f>
+        <v>-1471084.2</v>
+      </c>
+      <c r="G83" s="179"/>
     </row>
     <row r="84" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A84" s="107" t="s">
-        <v>55</v>
-      </c>
-      <c r="B84" s="86">
-        <v>-2873</v>
-      </c>
+      <c r="A84" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="B84" s="62">
+        <f>-(B74)</f>
+        <v>0</v>
+      </c>
+      <c r="G84" s="179"/>
     </row>
     <row r="85" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A85" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="B85" s="86">
-        <f>-B73</f>
-        <v>-1471136.43</v>
-      </c>
-    </row>
-    <row r="86" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A86" s="10" t="s">
-        <v>32</v>
-      </c>
-      <c r="B86" s="62">
-        <f>-(B74)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="87" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A87" s="108" t="s">
+      <c r="A85" s="108" t="s">
         <v>8</v>
       </c>
-      <c r="B87" s="76">
-        <f>SUM(B80:B86)</f>
-        <v>614741.73000000021</v>
-      </c>
-      <c r="D87" s="25"/>
-    </row>
-    <row r="88" spans="1:12" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B88" s="24"/>
-      <c r="C88" s="25"/>
-    </row>
-    <row r="90" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A90" s="147" t="s">
+      <c r="B85" s="76">
+        <f>SUM(B80:B84)</f>
+        <v>483066.42000000039</v>
+      </c>
+      <c r="C85" s="25"/>
+      <c r="D85" s="25"/>
+      <c r="G85" s="179"/>
+    </row>
+    <row r="86" spans="1:12" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B86" s="24"/>
+      <c r="C86" s="25"/>
+    </row>
+    <row r="88" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A88" s="148" t="s">
         <v>38</v>
       </c>
-      <c r="B90" s="147"/>
-    </row>
-    <row r="91" spans="1:12" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A91" s="147"/>
-      <c r="B91" s="147"/>
-    </row>
-    <row r="92" spans="1:12" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A92" s="74"/>
-      <c r="B92" s="18"/>
-    </row>
-    <row r="93" spans="1:12" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A93" s="74"/>
-      <c r="B93" s="18"/>
-    </row>
-    <row r="94" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A94" s="26" t="s">
+      <c r="B88" s="148"/>
+    </row>
+    <row r="89" spans="1:12" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A89" s="148"/>
+      <c r="B89" s="148"/>
+    </row>
+    <row r="90" spans="1:12" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A90" s="74"/>
+      <c r="B90" s="18"/>
+    </row>
+    <row r="91" spans="1:12" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A91" s="74"/>
+      <c r="B91" s="18"/>
+    </row>
+    <row r="92" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A92" s="26" t="s">
         <v>8</v>
       </c>
-      <c r="B94" s="75">
-        <f>SUM(B92:B93)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="95" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="L95" s="4"/>
+      <c r="B92" s="75">
+        <f>SUM(B90:B91)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="L93" s="4"/>
     </row>
   </sheetData>
-  <mergeCells count="9">
+  <mergeCells count="10">
+    <mergeCell ref="G80:G85"/>
     <mergeCell ref="A4:B7"/>
     <mergeCell ref="A14:D17"/>
     <mergeCell ref="A56:C56"/>
-    <mergeCell ref="A90:B91"/>
+    <mergeCell ref="A88:B89"/>
     <mergeCell ref="A63:B63"/>
     <mergeCell ref="A62:B62"/>
     <mergeCell ref="B9:B11"/>
@@ -2543,28 +2536,28 @@
   <sheetData>
     <row r="1" spans="1:18" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3"/>
-      <c r="B1" s="168" t="str">
+      <c r="B1" s="156" t="str">
         <f>RESUMEN!A4</f>
         <v>Banco: Santander
 C.U.I.T.   30-71774143-5
 CBU: 0720533020000000956840 ALIAS: BLONDA.LAGO.CORO
 Nº de cuenta: 533-009568/4</v>
       </c>
-      <c r="C1" s="169"/>
-      <c r="D1" s="169"/>
-      <c r="E1" s="170"/>
-      <c r="F1" s="168" t="s">
-        <v>113</v>
-      </c>
-      <c r="G1" s="169"/>
-      <c r="H1" s="169"/>
-      <c r="I1" s="170"/>
-      <c r="J1" s="164" t="s">
+      <c r="C1" s="157"/>
+      <c r="D1" s="157"/>
+      <c r="E1" s="158"/>
+      <c r="F1" s="156" t="s">
+        <v>111</v>
+      </c>
+      <c r="G1" s="157"/>
+      <c r="H1" s="157"/>
+      <c r="I1" s="158"/>
+      <c r="J1" s="152" t="s">
+        <v>108</v>
+      </c>
+      <c r="K1" s="153"/>
+      <c r="L1" s="114" t="s">
         <v>109</v>
-      </c>
-      <c r="K1" s="165"/>
-      <c r="L1" s="114" t="s">
-        <v>110</v>
       </c>
       <c r="M1" s="114"/>
       <c r="N1" s="116">
@@ -2576,103 +2569,103 @@
     </row>
     <row r="2" spans="1:18" ht="43.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="3"/>
-      <c r="B2" s="171"/>
-      <c r="C2" s="172"/>
-      <c r="D2" s="172"/>
-      <c r="E2" s="173"/>
-      <c r="F2" s="171"/>
-      <c r="G2" s="172"/>
-      <c r="H2" s="172"/>
-      <c r="I2" s="173"/>
-      <c r="J2" s="166"/>
-      <c r="K2" s="167"/>
+      <c r="B2" s="159"/>
+      <c r="C2" s="160"/>
+      <c r="D2" s="160"/>
+      <c r="E2" s="161"/>
+      <c r="F2" s="159"/>
+      <c r="G2" s="160"/>
+      <c r="H2" s="160"/>
+      <c r="I2" s="161"/>
+      <c r="J2" s="154"/>
+      <c r="K2" s="155"/>
       <c r="L2" s="115" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="M2" s="115"/>
       <c r="N2" s="95"/>
       <c r="O2" s="110"/>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A3" s="174" t="s">
+      <c r="A3" s="162" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="176" t="s">
+      <c r="B3" s="164" t="s">
+        <v>57</v>
+      </c>
+      <c r="C3" s="166" t="s">
         <v>58</v>
       </c>
-      <c r="C3" s="154" t="s">
-        <v>59</v>
-      </c>
-      <c r="D3" s="154" t="s">
+      <c r="D3" s="166" t="s">
         <v>5</v>
       </c>
-      <c r="E3" s="154" t="s">
+      <c r="E3" s="166" t="s">
         <v>17</v>
       </c>
-      <c r="F3" s="154" t="s">
+      <c r="F3" s="166" t="s">
         <v>46</v>
       </c>
-      <c r="G3" s="154" t="s">
+      <c r="G3" s="166" t="s">
         <v>6</v>
       </c>
-      <c r="H3" s="154" t="s">
+      <c r="H3" s="166" t="s">
         <v>35</v>
       </c>
-      <c r="I3" s="159" t="s">
+      <c r="I3" s="174" t="s">
         <v>36</v>
       </c>
-      <c r="J3" s="156" t="s">
+      <c r="J3" s="172" t="s">
         <v>34</v>
       </c>
-      <c r="K3" s="156" t="s">
+      <c r="K3" s="172" t="s">
         <v>7</v>
       </c>
-      <c r="L3" s="156" t="s">
+      <c r="L3" s="172" t="s">
         <v>33</v>
       </c>
-      <c r="M3" s="162" t="s">
+      <c r="M3" s="177" t="s">
         <v>44</v>
       </c>
       <c r="N3" s="34" t="s">
         <v>43</v>
       </c>
-      <c r="O3" s="151" t="s">
+      <c r="O3" s="168" t="s">
         <v>42</v>
       </c>
       <c r="R3" s="25"/>
     </row>
     <row r="4" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="175"/>
-      <c r="B4" s="177"/>
-      <c r="C4" s="158"/>
-      <c r="D4" s="158"/>
-      <c r="E4" s="155"/>
-      <c r="F4" s="158"/>
-      <c r="G4" s="158"/>
-      <c r="H4" s="155"/>
-      <c r="I4" s="160"/>
-      <c r="J4" s="157"/>
-      <c r="K4" s="161"/>
-      <c r="L4" s="157"/>
-      <c r="M4" s="163"/>
+      <c r="A4" s="163"/>
+      <c r="B4" s="165"/>
+      <c r="C4" s="167"/>
+      <c r="D4" s="167"/>
+      <c r="E4" s="171"/>
+      <c r="F4" s="167"/>
+      <c r="G4" s="167"/>
+      <c r="H4" s="171"/>
+      <c r="I4" s="175"/>
+      <c r="J4" s="173"/>
+      <c r="K4" s="176"/>
+      <c r="L4" s="173"/>
+      <c r="M4" s="178"/>
       <c r="N4" s="32" t="str">
         <f>RESUMEN!B9</f>
         <v>VTO 18/06</v>
       </c>
-      <c r="O4" s="152"/>
+      <c r="O4" s="169"/>
     </row>
     <row r="5" spans="1:18" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B5" s="35" t="s">
+        <v>59</v>
+      </c>
+      <c r="C5" s="35" t="s">
         <v>60</v>
       </c>
-      <c r="C5" s="35" t="s">
+      <c r="D5" s="102" t="s">
         <v>61</v>
-      </c>
-      <c r="D5" s="102" t="s">
-        <v>62</v>
       </c>
       <c r="E5" s="36">
         <v>6.84</v>
@@ -2715,7 +2708,7 @@
         <v>0.01</v>
       </c>
       <c r="Q5" s="25" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
     </row>
     <row r="6" spans="1:18" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
@@ -2723,13 +2716,13 @@
         <v>9</v>
       </c>
       <c r="B6" s="103" t="s">
+        <v>62</v>
+      </c>
+      <c r="C6" s="103" t="s">
         <v>63</v>
       </c>
-      <c r="C6" s="103" t="s">
+      <c r="D6" s="96" t="s">
         <v>64</v>
-      </c>
-      <c r="D6" s="96" t="s">
-        <v>65</v>
       </c>
       <c r="E6" s="104">
         <v>7.79</v>
@@ -2774,7 +2767,7 @@
         <v>0.02</v>
       </c>
       <c r="Q6" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
     </row>
     <row r="7" spans="1:18" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
@@ -2782,13 +2775,13 @@
         <v>10</v>
       </c>
       <c r="B7" s="103" t="s">
+        <v>65</v>
+      </c>
+      <c r="C7" s="103" t="s">
         <v>66</v>
       </c>
-      <c r="C7" s="103" t="s">
+      <c r="D7" s="103" t="s">
         <v>67</v>
-      </c>
-      <c r="D7" s="103" t="s">
-        <v>68</v>
       </c>
       <c r="E7" s="104">
         <v>6.75</v>
@@ -2833,7 +2826,7 @@
         <v>0.03</v>
       </c>
       <c r="Q7" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="R7" s="25"/>
     </row>
@@ -2842,13 +2835,13 @@
         <v>10</v>
       </c>
       <c r="B8" s="103" t="s">
+        <v>68</v>
+      </c>
+      <c r="C8" s="103" t="s">
         <v>69</v>
       </c>
-      <c r="C8" s="103" t="s">
+      <c r="D8" s="103" t="s">
         <v>70</v>
-      </c>
-      <c r="D8" s="103" t="s">
-        <v>71</v>
       </c>
       <c r="E8" s="104">
         <v>7.41</v>
@@ -2893,7 +2886,7 @@
         <v>0.04</v>
       </c>
       <c r="Q8" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="R8" s="25"/>
     </row>
@@ -2902,13 +2895,13 @@
         <v>11</v>
       </c>
       <c r="B9" s="103" t="s">
+        <v>71</v>
+      </c>
+      <c r="C9" s="103" t="s">
         <v>72</v>
       </c>
-      <c r="C9" s="103" t="s">
+      <c r="D9" s="103" t="s">
         <v>73</v>
-      </c>
-      <c r="D9" s="103" t="s">
-        <v>74</v>
       </c>
       <c r="E9" s="111">
         <v>8</v>
@@ -2952,7 +2945,7 @@
         <v>0.05</v>
       </c>
       <c r="Q9" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
     </row>
     <row r="10" spans="1:18" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
@@ -2960,13 +2953,13 @@
         <v>11</v>
       </c>
       <c r="B10" s="102" t="s">
+        <v>74</v>
+      </c>
+      <c r="C10" s="103" t="s">
         <v>75</v>
       </c>
-      <c r="C10" s="103" t="s">
+      <c r="D10" s="103" t="s">
         <v>76</v>
-      </c>
-      <c r="D10" s="103" t="s">
-        <v>77</v>
       </c>
       <c r="E10" s="102">
         <v>6.97</v>
@@ -3017,13 +3010,13 @@
         <v>12</v>
       </c>
       <c r="B11" s="102" t="s">
+        <v>77</v>
+      </c>
+      <c r="C11" s="102" t="s">
         <v>78</v>
       </c>
-      <c r="C11" s="102" t="s">
+      <c r="D11" s="102" t="s">
         <v>79</v>
-      </c>
-      <c r="D11" s="102" t="s">
-        <v>80</v>
       </c>
       <c r="E11" s="105">
         <v>6.75</v>
@@ -3068,7 +3061,7 @@
         <v>7.0000000000000007E-2</v>
       </c>
       <c r="Q11" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="12" spans="1:18" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
@@ -3076,13 +3069,13 @@
         <v>12</v>
       </c>
       <c r="B12" s="102" t="s">
+        <v>80</v>
+      </c>
+      <c r="C12" s="102" t="s">
         <v>81</v>
       </c>
-      <c r="C12" s="102" t="s">
+      <c r="D12" s="102" t="s">
         <v>82</v>
-      </c>
-      <c r="D12" s="102" t="s">
-        <v>83</v>
       </c>
       <c r="E12" s="105">
         <v>7.79</v>
@@ -3132,13 +3125,13 @@
         <v>13</v>
       </c>
       <c r="B13" s="103" t="s">
+        <v>83</v>
+      </c>
+      <c r="C13" s="103" t="s">
         <v>84</v>
       </c>
-      <c r="C13" s="103" t="s">
+      <c r="D13" s="103" t="s">
         <v>85</v>
-      </c>
-      <c r="D13" s="103" t="s">
-        <v>86</v>
       </c>
       <c r="E13" s="104">
         <v>7.62</v>
@@ -3183,7 +3176,7 @@
         <v>0.09</v>
       </c>
       <c r="Q13" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="14" spans="1:18" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
@@ -3191,13 +3184,13 @@
         <v>13</v>
       </c>
       <c r="B14" s="102" t="s">
+        <v>86</v>
+      </c>
+      <c r="C14" s="102" t="s">
         <v>87</v>
       </c>
-      <c r="C14" s="102" t="s">
-        <v>88</v>
-      </c>
       <c r="D14" s="102" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E14" s="105">
         <v>6.97</v>
@@ -3247,13 +3240,13 @@
         <v>14</v>
       </c>
       <c r="B15" s="102" t="s">
+        <v>88</v>
+      </c>
+      <c r="C15" s="102" t="s">
         <v>89</v>
       </c>
-      <c r="C15" s="102" t="s">
+      <c r="D15" s="102" t="s">
         <v>90</v>
-      </c>
-      <c r="D15" s="102" t="s">
-        <v>91</v>
       </c>
       <c r="E15" s="105">
         <v>14.01</v>
@@ -3298,7 +3291,7 @@
         <v>0.10999999999999999</v>
       </c>
       <c r="Q15" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
     </row>
     <row r="16" spans="1:18" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
@@ -3306,13 +3299,13 @@
         <v>14</v>
       </c>
       <c r="B16" s="102" t="s">
+        <v>91</v>
+      </c>
+      <c r="C16" s="102" t="s">
         <v>92</v>
       </c>
-      <c r="C16" s="102" t="s">
+      <c r="D16" s="102" t="s">
         <v>93</v>
-      </c>
-      <c r="D16" s="102" t="s">
-        <v>94</v>
       </c>
       <c r="E16" s="105">
         <v>13.1</v>
@@ -3357,7 +3350,7 @@
         <v>0.11999999999999998</v>
       </c>
       <c r="Q16" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="17" spans="1:16" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -3427,94 +3420,87 @@
       <c r="D19" s="27"/>
     </row>
     <row r="20" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="D20" s="153" t="s">
-        <v>56</v>
-      </c>
-      <c r="E20" s="153"/>
-      <c r="F20" s="153"/>
-      <c r="G20" s="153"/>
-      <c r="H20" s="153"/>
-      <c r="I20" s="153"/>
-      <c r="J20" s="153"/>
-      <c r="K20" s="153"/>
-      <c r="L20" s="153"/>
-      <c r="M20" s="153"/>
-      <c r="N20" s="153"/>
+      <c r="D20" s="170" t="s">
+        <v>55</v>
+      </c>
+      <c r="E20" s="170"/>
+      <c r="F20" s="170"/>
+      <c r="G20" s="170"/>
+      <c r="H20" s="170"/>
+      <c r="I20" s="170"/>
+      <c r="J20" s="170"/>
+      <c r="K20" s="170"/>
+      <c r="L20" s="170"/>
+      <c r="M20" s="170"/>
+      <c r="N20" s="170"/>
     </row>
     <row r="21" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="D21" s="153"/>
-      <c r="E21" s="153"/>
-      <c r="F21" s="153"/>
-      <c r="G21" s="153"/>
-      <c r="H21" s="153"/>
-      <c r="I21" s="153"/>
-      <c r="J21" s="153"/>
-      <c r="K21" s="153"/>
-      <c r="L21" s="153"/>
-      <c r="M21" s="153"/>
-      <c r="N21" s="153"/>
+      <c r="D21" s="170"/>
+      <c r="E21" s="170"/>
+      <c r="F21" s="170"/>
+      <c r="G21" s="170"/>
+      <c r="H21" s="170"/>
+      <c r="I21" s="170"/>
+      <c r="J21" s="170"/>
+      <c r="K21" s="170"/>
+      <c r="L21" s="170"/>
+      <c r="M21" s="170"/>
+      <c r="N21" s="170"/>
     </row>
     <row r="22" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="D22" s="153"/>
-      <c r="E22" s="153"/>
-      <c r="F22" s="153"/>
-      <c r="G22" s="153"/>
-      <c r="H22" s="153"/>
-      <c r="I22" s="153"/>
-      <c r="J22" s="153"/>
-      <c r="K22" s="153"/>
-      <c r="L22" s="153"/>
-      <c r="M22" s="153"/>
-      <c r="N22" s="153"/>
+      <c r="D22" s="170"/>
+      <c r="E22" s="170"/>
+      <c r="F22" s="170"/>
+      <c r="G22" s="170"/>
+      <c r="H22" s="170"/>
+      <c r="I22" s="170"/>
+      <c r="J22" s="170"/>
+      <c r="K22" s="170"/>
+      <c r="L22" s="170"/>
+      <c r="M22" s="170"/>
+      <c r="N22" s="170"/>
     </row>
     <row r="23" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="D23" s="153"/>
-      <c r="E23" s="153"/>
-      <c r="F23" s="153"/>
-      <c r="G23" s="153"/>
-      <c r="H23" s="153"/>
-      <c r="I23" s="153"/>
-      <c r="J23" s="153"/>
-      <c r="K23" s="153"/>
-      <c r="L23" s="153"/>
-      <c r="M23" s="153"/>
-      <c r="N23" s="153"/>
+      <c r="D23" s="170"/>
+      <c r="E23" s="170"/>
+      <c r="F23" s="170"/>
+      <c r="G23" s="170"/>
+      <c r="H23" s="170"/>
+      <c r="I23" s="170"/>
+      <c r="J23" s="170"/>
+      <c r="K23" s="170"/>
+      <c r="L23" s="170"/>
+      <c r="M23" s="170"/>
+      <c r="N23" s="170"/>
     </row>
     <row r="24" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="D24" s="153"/>
-      <c r="E24" s="153"/>
-      <c r="F24" s="153"/>
-      <c r="G24" s="153"/>
-      <c r="H24" s="153"/>
-      <c r="I24" s="153"/>
-      <c r="J24" s="153"/>
-      <c r="K24" s="153"/>
-      <c r="L24" s="153"/>
-      <c r="M24" s="153"/>
-      <c r="N24" s="153"/>
+      <c r="D24" s="170"/>
+      <c r="E24" s="170"/>
+      <c r="F24" s="170"/>
+      <c r="G24" s="170"/>
+      <c r="H24" s="170"/>
+      <c r="I24" s="170"/>
+      <c r="J24" s="170"/>
+      <c r="K24" s="170"/>
+      <c r="L24" s="170"/>
+      <c r="M24" s="170"/>
+      <c r="N24" s="170"/>
     </row>
     <row r="25" spans="1:16" ht="4.9000000000000004" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D25" s="153"/>
-      <c r="E25" s="153"/>
-      <c r="F25" s="153"/>
-      <c r="G25" s="153"/>
-      <c r="H25" s="153"/>
-      <c r="I25" s="153"/>
-      <c r="J25" s="153"/>
-      <c r="K25" s="153"/>
-      <c r="L25" s="153"/>
-      <c r="M25" s="153"/>
-      <c r="N25" s="153"/>
+      <c r="D25" s="170"/>
+      <c r="E25" s="170"/>
+      <c r="F25" s="170"/>
+      <c r="G25" s="170"/>
+      <c r="H25" s="170"/>
+      <c r="I25" s="170"/>
+      <c r="J25" s="170"/>
+      <c r="K25" s="170"/>
+      <c r="L25" s="170"/>
+      <c r="M25" s="170"/>
+      <c r="N25" s="170"/>
     </row>
   </sheetData>
   <mergeCells count="18">
-    <mergeCell ref="J1:K2"/>
-    <mergeCell ref="B1:E2"/>
-    <mergeCell ref="F1:I2"/>
-    <mergeCell ref="A3:A4"/>
-    <mergeCell ref="B3:B4"/>
-    <mergeCell ref="C3:C4"/>
-    <mergeCell ref="D3:D4"/>
     <mergeCell ref="O3:O4"/>
     <mergeCell ref="D20:N25"/>
     <mergeCell ref="H3:H4"/>
@@ -3526,6 +3512,13 @@
     <mergeCell ref="L3:L4"/>
     <mergeCell ref="M3:M4"/>
     <mergeCell ref="E3:E4"/>
+    <mergeCell ref="J1:K2"/>
+    <mergeCell ref="B1:E2"/>
+    <mergeCell ref="F1:I2"/>
+    <mergeCell ref="A3:A4"/>
+    <mergeCell ref="B3:B4"/>
+    <mergeCell ref="C3:C4"/>
+    <mergeCell ref="D3:D4"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="3" orientation="landscape" r:id="rId1"/>
